--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,6 +1027,480 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121493557</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57720</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Västra Hästkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>635592</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6521415</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Edmert</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Edmert, Hans Norelius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121493547</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56404</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Västra Hästkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>635592</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6521415</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eva Edmert</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eva Edmert, Hans Norelius</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121493554</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57502</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Västra Hästkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>635592</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6521415</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eva Edmert</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eva Edmert, Hans Norelius</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121493561</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57785</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Västra Hästkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>635592</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6521415</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eva Edmert</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eva Edmert, Hans Norelius</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121493557</v>
+        <v>121493547</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>56404</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,16 +1045,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100045</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1064,7 +1064,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1145,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121493547</v>
+        <v>121493561</v>
       </c>
       <c r="B6" t="n">
-        <v>56404</v>
+        <v>57785</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,35 +1162,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100045</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1266,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121493554</v>
+        <v>121493557</v>
       </c>
       <c r="B7" t="n">
-        <v>57502</v>
+        <v>57720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,20 +1283,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1301,7 +1306,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1382,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121493561</v>
+        <v>121493554</v>
       </c>
       <c r="B8" t="n">
-        <v>57785</v>
+        <v>57502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,31 +1403,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>rastande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121493547</v>
+        <v>121493561</v>
       </c>
       <c r="B5" t="n">
-        <v>56404</v>
+        <v>57788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,35 +1041,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100045</v>
+        <v>102999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121493561</v>
+        <v>121493557</v>
       </c>
       <c r="B6" t="n">
-        <v>57785</v>
+        <v>57723</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,35 +1162,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1271,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121493557</v>
+        <v>121493554</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57505</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,20 +1278,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1306,7 +1301,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1387,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121493554</v>
+        <v>121493547</v>
       </c>
       <c r="B8" t="n">
-        <v>57502</v>
+        <v>56407</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,20 +1394,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>100045</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1422,7 +1417,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121493561</v>
+        <v>121493557</v>
       </c>
       <c r="B5" t="n">
-        <v>57788</v>
+        <v>57723</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,35 +1041,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121493557</v>
+        <v>121493561</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>57788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,30 +1157,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121493557</v>
+        <v>121493561</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,30 +1041,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1145,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121493561</v>
+        <v>121493554</v>
       </c>
       <c r="B6" t="n">
-        <v>57788</v>
+        <v>57506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,31 +1166,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>rastande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121493554</v>
+        <v>121493557</v>
       </c>
       <c r="B7" t="n">
-        <v>57505</v>
+        <v>57724</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,20 +1278,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1385,7 +1385,7 @@
         <v>121493547</v>
       </c>
       <c r="B8" t="n">
-        <v>56407</v>
+        <v>56408</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121493561</v>
+        <v>121493557</v>
       </c>
       <c r="B5" t="n">
-        <v>57789</v>
+        <v>57725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,35 +1041,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121493554</v>
+        <v>121493547</v>
       </c>
       <c r="B6" t="n">
-        <v>57506</v>
+        <v>56409</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,20 +1157,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>100045</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1185,7 +1180,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121493557</v>
+        <v>121493561</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>57790</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,30 +1278,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1382,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121493547</v>
+        <v>121493554</v>
       </c>
       <c r="B8" t="n">
-        <v>56408</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,20 +1399,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100045</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1417,12 +1422,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121493547</v>
+        <v>121493554</v>
       </c>
       <c r="B6" t="n">
-        <v>56409</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100045</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1180,12 +1180,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1266,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121493561</v>
+        <v>121493547</v>
       </c>
       <c r="B7" t="n">
-        <v>57790</v>
+        <v>56409</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,35 +1273,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102999</v>
+        <v>100045</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1387,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121493554</v>
+        <v>121493561</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>57790</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,26 +1398,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121493557</v>
+        <v>121493547</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>56409</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,16 +1045,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100045</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1064,7 +1064,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1145,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121493554</v>
+        <v>121493561</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>57790</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,26 +1166,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1261,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121493547</v>
+        <v>121493554</v>
       </c>
       <c r="B7" t="n">
-        <v>56409</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,20 +1283,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100045</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1296,12 +1306,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1382,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121493561</v>
+        <v>121493557</v>
       </c>
       <c r="B8" t="n">
-        <v>57790</v>
+        <v>57725</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,35 +1399,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121493547</v>
+        <v>121493561</v>
       </c>
       <c r="B5" t="n">
-        <v>56409</v>
+        <v>57790</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,35 +1041,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100045</v>
+        <v>102999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121493561</v>
+        <v>121493547</v>
       </c>
       <c r="B6" t="n">
-        <v>57790</v>
+        <v>56409</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,35 +1162,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102999</v>
+        <v>100045</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121493561</v>
+        <v>121493557</v>
       </c>
       <c r="B5" t="n">
-        <v>57790</v>
+        <v>57726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,35 +1041,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121493547</v>
+        <v>121493561</v>
       </c>
       <c r="B6" t="n">
-        <v>56409</v>
+        <v>57791</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,35 +1157,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100045</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1274,7 +1269,7 @@
         <v>121493554</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1387,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121493557</v>
+        <v>121493547</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>56410</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,16 +1398,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100045</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1422,7 +1417,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121493554</v>
+        <v>121493557</v>
       </c>
       <c r="B5" t="n">
-        <v>57508</v>
+        <v>57726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,20 +1041,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121493557</v>
+        <v>121493547</v>
       </c>
       <c r="B6" t="n">
-        <v>57726</v>
+        <v>56410</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,16 +1161,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100045</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1180,7 +1180,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1261,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121493561</v>
+        <v>121493554</v>
       </c>
       <c r="B7" t="n">
-        <v>57791</v>
+        <v>57508</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,31 +1282,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>rastande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121493547</v>
+        <v>121493561</v>
       </c>
       <c r="B8" t="n">
-        <v>56410</v>
+        <v>57791</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,35 +1394,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100045</v>
+        <v>102999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121493547</v>
+        <v>121493561</v>
       </c>
       <c r="B6" t="n">
-        <v>56410</v>
+        <v>57791</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,35 +1157,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100045</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121493561</v>
+        <v>121493547</v>
       </c>
       <c r="B8" t="n">
-        <v>57791</v>
+        <v>56410</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,35 +1394,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102999</v>
+        <v>100045</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">

--- a/artfynd/A 18443-2019 artfynd.xlsx
+++ b/artfynd/A 18443-2019 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121493557</v>
+        <v>121493554</v>
       </c>
       <c r="B5" t="n">
-        <v>57726</v>
+        <v>57508</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,20 +1041,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121493561</v>
+        <v>121493547</v>
       </c>
       <c r="B6" t="n">
-        <v>57791</v>
+        <v>56410</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,35 +1157,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102999</v>
+        <v>100045</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121493554</v>
+        <v>121493561</v>
       </c>
       <c r="B7" t="n">
-        <v>57508</v>
+        <v>57791</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,26 +1282,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1382,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121493547</v>
+        <v>121493557</v>
       </c>
       <c r="B8" t="n">
-        <v>56410</v>
+        <v>57726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,16 +1403,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100045</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1417,12 +1422,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
